--- a/data/trans_dic/IP29_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,5; 42,46</t>
+          <t>26,15; 42,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,85; 33,14</t>
+          <t>17,79; 32,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 36,24</t>
+          <t>18,44; 37,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,8; 41,92</t>
+          <t>26,19; 41,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,55; 37,27</t>
+          <t>20,62; 37,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 31,29</t>
+          <t>15,18; 32,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 39,86</t>
+          <t>28,33; 39,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 32,12</t>
+          <t>21,09; 32,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 30,76</t>
+          <t>18,32; 30,81</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,62; 37,22</t>
+          <t>29,82; 37,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,15; 30,23</t>
+          <t>23,12; 29,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,32; 32,05</t>
+          <t>25,14; 32,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 29,93</t>
+          <t>23,63; 30,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,87; 27,48</t>
+          <t>20,69; 27,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,94; 33,98</t>
+          <t>26,83; 33,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,43; 32,47</t>
+          <t>27,56; 32,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 27,52</t>
+          <t>23,04; 27,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 32,03</t>
+          <t>27,16; 32,22</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 31,09</t>
+          <t>19,84; 30,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,81; 35,9</t>
+          <t>23,46; 35,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,75; 37,12</t>
+          <t>25,39; 37,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,45; 38,31</t>
+          <t>25,68; 37,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,8</t>
+          <t>16,17; 26,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,85; 39,38</t>
+          <t>27,45; 38,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 32,45</t>
+          <t>23,88; 32,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,19; 29,42</t>
+          <t>20,85; 29,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,21; 36,29</t>
+          <t>28,32; 36,44</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,5; 34,17</t>
+          <t>28,75; 34,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,09; 29,57</t>
+          <t>24,47; 29,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,45; 32,11</t>
+          <t>26,39; 31,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,11; 31,46</t>
+          <t>26,02; 31,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,33</t>
+          <t>20,92; 26,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 33,49</t>
+          <t>27,66; 33,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,14; 32,3</t>
+          <t>27,89; 31,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,44; 27,4</t>
+          <t>23,37; 27,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,83; 31,77</t>
+          <t>27,68; 31,76</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30280</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22301</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15588</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27980</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22866</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15026</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58260</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>45167</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>30614</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>23205; 37635</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16061; 29287</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10712; 21773</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21867; 34961</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16907; 30451</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10186; 21537</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>48788; 68547</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>36343; 55481</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>22935; 38572</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>133029</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>118400</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>132164</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>123507</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>115453</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>145935</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>256536</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>233854</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>278100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>118721; 147937</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>102415; 132648</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>116072; 147746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108667; 140685</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>99980; 131565</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>128523; 161760</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>236462; 280024</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>213396; 257124</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>255525; 303089</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>41790</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52029</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>47348</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35523</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59793</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89138</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>82732</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>111821</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>32925; 51132</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37988; 57612</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42285; 61851</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38868; 56953</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>27085; 44168</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>49679; 70543</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>75771; 102740</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>68686; 96072</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>98415; 126657</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>205100</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187911</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>199781</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>198835</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>173843</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>403934</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>361753</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>187669; 226564</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170146; 207315</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181116; 217984</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>180742; 218377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>153260; 192415</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>201162; 240839</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>375757; 430980</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>333657; 389299</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>391273; 448977</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP29_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,15; 42,4</t>
+          <t>26,45; 42,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 32,43</t>
+          <t>17,82; 32,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,44; 37,47</t>
+          <t>17,99; 36,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,19; 41,88</t>
+          <t>26,15; 42,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 37,14</t>
+          <t>19,8; 37,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,18; 32,1</t>
+          <t>14,18; 31,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 39,8</t>
+          <t>28,18; 39,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,09; 32,2</t>
+          <t>20,68; 32,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 30,81</t>
+          <t>18,89; 31,63</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 37,16</t>
+          <t>30,05; 37,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,12; 29,95</t>
+          <t>23,58; 30,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,14; 32,0</t>
+          <t>25,41; 32,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,63; 30,59</t>
+          <t>23,96; 30,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 27,22</t>
+          <t>20,82; 27,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 33,77</t>
+          <t>27,03; 33,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,56; 32,64</t>
+          <t>27,71; 32,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 27,76</t>
+          <t>22,86; 27,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,16; 32,22</t>
+          <t>26,94; 31,9</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,84; 30,81</t>
+          <t>20,05; 31,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,46; 35,57</t>
+          <t>23,71; 35,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,39; 37,13</t>
+          <t>25,56; 37,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,68; 37,63</t>
+          <t>25,02; 37,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 26,37</t>
+          <t>16,43; 27,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,45; 38,98</t>
+          <t>27,8; 38,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,88; 32,38</t>
+          <t>24,18; 32,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 29,16</t>
+          <t>21,06; 28,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,32; 36,44</t>
+          <t>28,14; 36,44</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,75; 34,71</t>
+          <t>28,54; 34,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,82</t>
+          <t>24,12; 29,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,76</t>
+          <t>26,51; 31,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,02; 31,43</t>
+          <t>25,93; 31,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,92; 26,26</t>
+          <t>21,18; 26,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,66; 33,12</t>
+          <t>27,26; 33,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,89; 31,98</t>
+          <t>28,17; 32,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 27,26</t>
+          <t>23,33; 27,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 31,76</t>
+          <t>27,66; 31,72</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23205; 37635</t>
+          <t>23474; 37771</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16061; 29287</t>
+          <t>16089; 29720</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10712; 21773</t>
+          <t>10452; 21470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21867; 34961</t>
+          <t>21831; 35074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16907; 30451</t>
+          <t>16234; 30393</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10186; 21537</t>
+          <t>9515; 21422</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48788; 68547</t>
+          <t>48545; 67810</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36343; 55481</t>
+          <t>35623; 55619</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22935; 38572</t>
+          <t>23647; 39600</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>118721; 147937</t>
+          <t>119612; 148651</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>102415; 132648</t>
+          <t>104451; 135023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>116072; 147746</t>
+          <t>117328; 149399</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108667; 140685</t>
+          <t>110191; 139594</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>99980; 131565</t>
+          <t>100606; 131764</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>128523; 161760</t>
+          <t>129482; 162398</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>236462; 280024</t>
+          <t>237768; 278489</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>213396; 257124</t>
+          <t>211771; 256943</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255525; 303089</t>
+          <t>253457; 300107</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32925; 51132</t>
+          <t>33275; 52187</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37988; 57612</t>
+          <t>38393; 57265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42285; 61851</t>
+          <t>42584; 62304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38868; 56953</t>
+          <t>37876; 56842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27085; 44168</t>
+          <t>27516; 46165</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49679; 70543</t>
+          <t>50317; 70521</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75771; 102740</t>
+          <t>76741; 103159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68686; 96072</t>
+          <t>69375; 95257</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98415; 126657</t>
+          <t>97816; 126639</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>187669; 226564</t>
+          <t>186301; 225741</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>170146; 207315</t>
+          <t>167710; 207091</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181116; 217984</t>
+          <t>181939; 218783</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>180742; 218377</t>
+          <t>180134; 218099</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>153260; 192415</t>
+          <t>155226; 193932</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>201162; 240839</t>
+          <t>198247; 240145</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>375757; 430980</t>
+          <t>379559; 431631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>333657; 389299</t>
+          <t>333144; 388956</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>391273; 448977</t>
+          <t>390945; 448340</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP29_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>34,12%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>24,7%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26,83%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,45; 42,56</t>
+          <t>24,8; 41,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 32,91</t>
+          <t>20,55; 37,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 36,95</t>
+          <t>14,94; 31,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,15; 42,01</t>
+          <t>26,5; 42,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 37,07</t>
+          <t>17,85; 33,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 31,93</t>
+          <t>17,97; 36,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,18; 39,37</t>
+          <t>28,54; 39,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,68; 32,28</t>
+          <t>20,8; 32,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,89; 31,63</t>
+          <t>18,45; 30,76</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30,46%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>33,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>26,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>28,63%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,05; 37,34</t>
+          <t>23,83; 29,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,58; 30,48</t>
+          <t>20,87; 27,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,41; 32,36</t>
+          <t>26,94; 33,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 30,36</t>
+          <t>29,62; 37,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,82; 27,26</t>
+          <t>23,15; 30,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,9</t>
+          <t>25,32; 32,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,71; 32,46</t>
+          <t>27,43; 32,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,86; 27,74</t>
+          <t>22,73; 27,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,94; 31,9</t>
+          <t>26,93; 32,03</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>25,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>31,24%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,28%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 31,45</t>
+          <t>25,45; 38,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,71; 35,36</t>
+          <t>16,28; 27,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,56; 37,4</t>
+          <t>27,85; 39,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,02; 37,55</t>
+          <t>20,0; 31,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 27,57</t>
+          <t>23,81; 35,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,8; 38,96</t>
+          <t>25,75; 37,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,18; 32,51</t>
+          <t>23,92; 32,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,06; 28,92</t>
+          <t>21,19; 29,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,14; 36,44</t>
+          <t>28,21; 36,29</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,72%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,58</t>
+          <t>26,11; 31,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,12; 29,79</t>
+          <t>21,05; 26,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 31,88</t>
+          <t>27,57; 33,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,93; 31,39</t>
+          <t>28,5; 34,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 26,47</t>
+          <t>24,09; 29,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 33,03</t>
+          <t>26,45; 32,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,17; 32,03</t>
+          <t>28,14; 32,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,33; 27,24</t>
+          <t>23,44; 27,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,66; 31,72</t>
+          <t>27,83; 31,77</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27980</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15026</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>30280</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>22301</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15588</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27980</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>22866</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15026</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23474; 37771</t>
+          <t>20703; 35001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16089; 29720</t>
+          <t>16849; 30555</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10452; 21470</t>
+          <t>10021; 20991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21831; 35074</t>
+          <t>23519; 37687</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16234; 30393</t>
+          <t>16116; 29927</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9515; 21422</t>
+          <t>10439; 21054</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48545; 67810</t>
+          <t>49160; 68649</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35623; 55619</t>
+          <t>35829; 55331</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23647; 39600</t>
+          <t>23094; 38506</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>199</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>123507</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>115453</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145935</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>133029</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>118400</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>132164</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123507</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>115453</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>145935</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119612; 148651</t>
+          <t>109598; 137642</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>104451; 135023</t>
+          <t>100864; 132825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117328; 149399</t>
+          <t>129053; 162804</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110191; 139594</t>
+          <t>117890; 148175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100606; 131764</t>
+          <t>102563; 133893</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>129482; 162398</t>
+          <t>116908; 147949</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>237768; 278489</t>
+          <t>235286; 278555</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>211771; 256943</t>
+          <t>210506; 254932</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253457; 300107</t>
+          <t>253376; 301292</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47348</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35523</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59793</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>41790</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>47209</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>52029</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47348</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35523</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59793</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33275; 52187</t>
+          <t>38518; 57990</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38393; 57265</t>
+          <t>27263; 46561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42584; 62304</t>
+          <t>50398; 71281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37876; 56842</t>
+          <t>33195; 51597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27516; 46165</t>
+          <t>38565; 58136</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50317; 70521</t>
+          <t>42892; 61835</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76741; 103159</t>
+          <t>75918; 102979</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69375; 95257</t>
+          <t>69793; 96925</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97816; 126639</t>
+          <t>98045; 126127</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>269</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>301</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>198835</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173843</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>199781</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>198835</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>173843</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186301; 225741</t>
+          <t>181354; 218578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167710; 207091</t>
+          <t>154210; 192899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181939; 218783</t>
+          <t>200495; 243531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>180134; 218099</t>
+          <t>186056; 223047</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155226; 193932</t>
+          <t>167451; 205543</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>198247; 240145</t>
+          <t>181532; 220370</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>379559; 431631</t>
+          <t>379147; 435261</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>333144; 388956</t>
+          <t>334744; 391190</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>390945; 448340</t>
+          <t>393370; 449071</t>
         </is>
       </c>
     </row>
